--- a/data/trans_dic/Q20C_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Q20C_R2-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado</t>
+          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado (tasa de respuesta: 95,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,16; 73,43</t>
+          <t>11,51; 75,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,51; 100,0</t>
+          <t>13,68; 100,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,71</t>
+          <t>0,0; 78,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,23</t>
+          <t>0,0; 67,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -892,22 +892,22 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,07</t>
+          <t>0,0; 37,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,03</t>
+          <t>0,0; 58,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,57</t>
+          <t>0,0; 71,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,56</t>
+          <t>0,0; 40,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 92,59</t>
+          <t>0,0; 84,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,42</t>
+          <t>0,0; 54,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,3; 55,68</t>
+          <t>11,3; 57,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,69; 59,54</t>
+          <t>6,75; 59,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,35</t>
+          <t>0,0; 28,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,0; 42,69</t>
+          <t>9,58; 41,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,34</t>
+          <t>0,0; 24,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 53,95</t>
+          <t>8,55; 57,61</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>19,42; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,34; 61,29</t>
+          <t>8,34; 60,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,21; 78,03</t>
+          <t>10,84; 77,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,59; 64,17</t>
+          <t>9,82; 60,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,76</t>
+          <t>0,0; 58,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,14; 58,72</t>
+          <t>17,68; 61,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,14; 73,06</t>
+          <t>14,74; 72,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,77</t>
+          <t>0,0; 9,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,45; 63,91</t>
+          <t>13,46; 57,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,31; 54,91</t>
+          <t>20,52; 53,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19,28; 62,4</t>
+          <t>22,57; 65,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,91; 38,12</t>
+          <t>7,52; 39,21</t>
         </is>
       </c>
     </row>
@@ -1282,57 +1282,57 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,28</t>
+          <t>0,0; 56,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,33</t>
+          <t>0,0; 51,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,45; 49,07</t>
+          <t>9,61; 50,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,91</t>
+          <t>0,0; 54,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,74; 70,06</t>
+          <t>10,08; 70,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,52; 58,96</t>
+          <t>11,7; 63,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 41,95</t>
+          <t>5,26; 41,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,02</t>
+          <t>0,0; 31,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,06; 46,99</t>
+          <t>8,89; 48,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,3; 44,76</t>
+          <t>14,34; 46,31</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,44; 100,0</t>
+          <t>18,92; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,41; 67,14</t>
+          <t>8,0; 67,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,85</t>
+          <t>0,0; 61,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,48; 50,15</t>
+          <t>12,33; 49,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,63</t>
+          <t>0,0; 55,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,46; 62,35</t>
+          <t>8,46; 54,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,07; 48,66</t>
+          <t>7,11; 55,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,74; 75,3</t>
+          <t>12,9; 77,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,46; 63,02</t>
+          <t>12,07; 59,11</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,99; 47,8</t>
+          <t>12,98; 54,55</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,78; 43,24</t>
+          <t>8,48; 45,98</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,15; 49,25</t>
+          <t>18,6; 48,8</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,91</t>
+          <t>0,0; 67,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,0</t>
+          <t>0,0; 80,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,41; 33,83</t>
+          <t>3,48; 33,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,93</t>
+          <t>0,0; 61,49</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,9</t>
+          <t>0,0; 26,79</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 19,97</t>
+          <t>2,25; 20,63</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,05; 43,79</t>
+          <t>13,46; 42,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,37; 30,79</t>
+          <t>10,33; 31,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,87; 38,72</t>
+          <t>11,27; 35,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,12; 40,07</t>
+          <t>16,52; 38,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,14; 30,04</t>
+          <t>9,32; 30,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,96; 37,77</t>
+          <t>17,77; 37,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,52; 39,48</t>
+          <t>15,44; 38,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,24; 29,07</t>
+          <t>11,39; 29,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,61; 30,44</t>
+          <t>13,58; 31,82</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17,01; 32,48</t>
+          <t>17,14; 31,56</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16,72; 33,58</t>
+          <t>17,33; 34,35</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,63; 30,9</t>
+          <t>16,36; 30,6</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado</t>
+          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado (tasa de respuesta: 95,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 697</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>951; 6261</t>
+          <t>982; 6464</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>809; 5574</t>
+          <t>762; 5574</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2276,17 +2276,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1520</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3609</t>
+          <t>0; 3600</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1030</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3829</t>
+          <t>0; 3963</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2311,22 +2311,22 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1536</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4019</t>
+          <t>0; 4026</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 5250</t>
+          <t>0; 5600</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4656</t>
+          <t>0; 4661</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2484,32 +2484,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1539</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4727</t>
+          <t>0; 4916</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1706</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4618</t>
+          <t>0; 4226</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3525</t>
+          <t>0; 3423</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2023; 9965</t>
+          <t>2023; 10296</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2519,27 +2519,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>625; 4842</t>
+          <t>549; 4861</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4148</t>
+          <t>0; 3425</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3017; 12875</t>
+          <t>2888; 12381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4741</t>
+          <t>0; 4130</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>790; 7078</t>
+          <t>1122; 7558</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3806</t>
+          <t>739; 3806</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1055; 7751</t>
+          <t>1055; 7658</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1094; 7611</t>
+          <t>1058; 7558</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1401; 8493</t>
+          <t>1300; 8019</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5100</t>
+          <t>0; 5760</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4664; 15100</t>
+          <t>4547; 15825</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1919; 9262</t>
+          <t>1869; 9172</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 1207</t>
+          <t>0; 1110</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1838; 8729</t>
+          <t>1838; 7872</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7407; 21066</t>
+          <t>7872; 20524</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4325; 13998</t>
+          <t>5064; 14606</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1934; 9314</t>
+          <t>1838; 9581</t>
         </is>
       </c>
     </row>
@@ -2905,57 +2905,57 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5134</t>
+          <t>0; 5237</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 7939</t>
+          <t>0; 7314</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1274; 7393</t>
+          <t>1447; 7674</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5845</t>
+          <t>0; 5822</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1841</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1079; 7762</t>
+          <t>1117; 7827</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>745; 4618</t>
+          <t>916; 4961</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>993; 7864</t>
+          <t>986; 7783</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 6025</t>
+          <t>0; 6220</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2282; 11830</t>
+          <t>2237; 12157</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3274; 10251</t>
+          <t>3283; 10605</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>973; 5006</t>
+          <t>947; 5006</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>750; 6797</t>
+          <t>810; 6842</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5407</t>
+          <t>0; 5390</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1972; 7337</t>
+          <t>1803; 7235</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4645</t>
+          <t>0; 5485</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>939; 6918</t>
+          <t>939; 6045</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>860; 5922</t>
+          <t>866; 6799</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>604; 3571</t>
+          <t>612; 3662</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2464; 9432</t>
+          <t>1807; 8847</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2121; 10143</t>
+          <t>2754; 11575</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1835; 9042</t>
+          <t>1773; 9614</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3516; 9541</t>
+          <t>3603; 9453</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1184</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 1949</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3009</t>
+          <t>0; 3125</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 950</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4423</t>
+          <t>0; 4424</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 1769</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2223</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>320; 3171</t>
+          <t>326; 3133</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5158</t>
+          <t>0; 5040</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 2050</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 5381</t>
+          <t>0; 3804</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>323; 2885</t>
+          <t>325; 2980</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4680; 14587</t>
+          <t>4484; 14136</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5604; 18409</t>
+          <t>6173; 18557</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6087; 19857</t>
+          <t>5778; 18392</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9714; 22730</t>
+          <t>9372; 21865</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3990; 14723</t>
+          <t>4570; 14833</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14580; 30653</t>
+          <t>14419; 30731</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9952; 23784</t>
+          <t>9300; 23282</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4944; 12785</t>
+          <t>5009; 12850</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>11208; 25061</t>
+          <t>11181; 26193</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>23978; 45776</t>
+          <t>24158; 44475</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>18642; 37453</t>
+          <t>19332; 38315</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>15738; 31122</t>
+          <t>16474; 30813</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q20C_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Q20C_R2-Edad-trans_dic.xlsx
@@ -762,12 +762,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,51; 75,8</t>
+          <t>11,7; 75,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,68; 100,0</t>
+          <t>15,2; 100,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,51</t>
+          <t>0,0; 66,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,52</t>
+          <t>0,0; 69,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,79</t>
+          <t>0,0; 78,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -897,22 +897,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,14</t>
+          <t>0,0; 38,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,7</t>
+          <t>0,0; 49,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,64</t>
+          <t>0,0; 71,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,98</t>
+          <t>0,0; 79,2</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,1</t>
+          <t>0,0; 36,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 84,74</t>
+          <t>0,0; 84,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,79</t>
+          <t>0,0; 55,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,3; 57,52</t>
+          <t>10,95; 57,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,83</t>
+          <t>0,0; 57,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 59,78</t>
+          <t>7,24; 56,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,37</t>
+          <t>0,0; 33,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,58; 41,05</t>
+          <t>10,36; 42,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,69</t>
+          <t>0,0; 25,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,55; 57,61</t>
+          <t>5,73; 50,45</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,42; 100,0</t>
+          <t>7,44; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,34; 60,57</t>
+          <t>8,23; 61,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,84; 77,48</t>
+          <t>10,89; 77,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,82; 60,59</t>
+          <t>18,57; 73,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,45</t>
+          <t>0,0; 54,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,68; 61,54</t>
+          <t>19,25; 61,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,74; 72,35</t>
+          <t>15,17; 73,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,91</t>
+          <t>0,0; 31,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,46; 57,63</t>
+          <t>13,35; 63,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,52; 53,5</t>
+          <t>19,52; 52,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22,57; 65,11</t>
+          <t>22,44; 63,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 39,21</t>
+          <t>14,47; 50,04</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -1277,27 +1277,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,32</t>
+          <t>0,0; 58,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,39</t>
+          <t>0,0; 55,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,89</t>
+          <t>0,0; 55,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,61; 50,93</t>
+          <t>7,61; 45,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,69</t>
+          <t>0,0; 46,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,08; 70,64</t>
+          <t>9,88; 70,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,7; 63,34</t>
+          <t>12,45; 58,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,26; 41,51</t>
+          <t>5,24; 45,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,0</t>
+          <t>0,0; 30,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,89; 48,29</t>
+          <t>8,89; 49,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,34; 46,31</t>
+          <t>14,04; 42,22</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,92; 100,0</t>
+          <t>19,18; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,0; 67,58</t>
+          <t>8,62; 68,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,66</t>
+          <t>0,0; 62,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,33; 49,46</t>
+          <t>11,2; 48,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,06</t>
+          <t>0,0; 46,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,46; 54,49</t>
+          <t>8,43; 54,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,11; 55,87</t>
+          <t>7,0; 54,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,9; 77,23</t>
+          <t>10,78; 72,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,07; 59,11</t>
+          <t>12,45; 64,4</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,98; 54,55</t>
+          <t>10,56; 50,36</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,48; 45,98</t>
+          <t>8,81; 44,9</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,6; 48,8</t>
+          <t>17,08; 49,09</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,42</t>
+          <t>0,0; 60,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,01</t>
+          <t>0,0; 81,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,48; 33,42</t>
+          <t>3,21; 29,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,49</t>
+          <t>0,0; 53,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,79</t>
+          <t>0,0; 25,65</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 20,63</t>
+          <t>2,17; 19,36</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,46; 42,44</t>
+          <t>13,49; 44,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,33; 31,04</t>
+          <t>10,52; 32,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,27; 35,87</t>
+          <t>11,01; 35,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,52; 38,54</t>
+          <t>18,9; 40,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,32; 30,26</t>
+          <t>8,32; 30,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,77; 37,86</t>
+          <t>17,42; 37,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,44; 38,64</t>
+          <t>16,25; 39,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,39; 29,22</t>
+          <t>12,33; 28,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,58; 31,82</t>
+          <t>13,24; 31,22</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17,14; 31,56</t>
+          <t>16,95; 31,65</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17,33; 34,35</t>
+          <t>17,23; 33,82</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,36; 30,6</t>
+          <t>17,57; 33,27</t>
         </is>
       </c>
     </row>
@@ -2113,12 +2113,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>982; 6464</t>
+          <t>997; 6431</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>762; 5574</t>
+          <t>847; 5574</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1202</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3600</t>
+          <t>0; 3053</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3741</t>
+          <t>0; 3698</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3963</t>
+          <t>0; 4095</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3954</t>
+          <t>0; 3886</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2316,22 +2316,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4026</t>
+          <t>0; 4122</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 5600</t>
+          <t>0; 4750</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4661</t>
+          <t>0; 4658</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 5278</t>
+          <t>0; 5176</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3625</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4916</t>
+          <t>0; 4493</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2499,47 +2499,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4226</t>
+          <t>0; 5033</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3423</t>
+          <t>0; 3451</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2023; 10296</t>
+          <t>1960; 10291</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4183</t>
+          <t>0; 4416</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>549; 4861</t>
+          <t>637; 4954</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3425</t>
+          <t>0; 4094</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2888; 12381</t>
+          <t>3124; 12692</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4130</t>
+          <t>0; 4200</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1122; 7558</t>
+          <t>845; 7439</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>7436</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>8816</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>739; 3806</t>
+          <t>283; 3806</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1055; 7658</t>
+          <t>1040; 7760</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1058; 7558</t>
+          <t>1063; 7600</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1300; 8019</t>
+          <t>3110; 12313</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5760</t>
+          <t>0; 5363</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4547; 15825</t>
+          <t>4950; 15886</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1869; 9172</t>
+          <t>1923; 9258</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 1110</t>
+          <t>0; 4125</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1838; 7872</t>
+          <t>1823; 8613</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7872; 20524</t>
+          <t>7487; 20257</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5064; 14606</t>
+          <t>5033; 14338</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1838; 9581</t>
+          <t>4308; 14901</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>6929</t>
         </is>
       </c>
     </row>
@@ -2900,27 +2900,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4724</t>
+          <t>0; 4706</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5237</t>
+          <t>0; 5146</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 7314</t>
+          <t>0; 7885</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1447; 7674</t>
+          <t>1197; 7191</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5822</t>
+          <t>0; 4992</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2930,32 +2930,32 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1117; 7827</t>
+          <t>1095; 7777</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>916; 4961</t>
+          <t>1264; 5902</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>986; 7783</t>
+          <t>983; 8600</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 6220</t>
+          <t>0; 6052</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2237; 12157</t>
+          <t>2238; 12388</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3283; 10605</t>
+          <t>3632; 10921</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>6271</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>947; 5006</t>
+          <t>960; 5006</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>810; 6842</t>
+          <t>872; 6929</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5390</t>
+          <t>0; 5427</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1803; 7235</t>
+          <t>1704; 7419</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5485</t>
+          <t>0; 4676</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>939; 6045</t>
+          <t>935; 6081</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>866; 6799</t>
+          <t>851; 6675</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>612; 3662</t>
+          <t>592; 3976</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1807; 8847</t>
+          <t>1863; 9639</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2754; 11575</t>
+          <t>2242; 10687</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1773; 9614</t>
+          <t>1842; 9389</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3603; 9453</t>
+          <t>3537; 10165</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1204</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3125</t>
+          <t>0; 2809</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4424</t>
+          <t>0; 4492</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>326; 3133</t>
+          <t>342; 3111</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5040</t>
+          <t>0; 4403</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 3804</t>
+          <t>0; 3642</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>325; 2980</t>
+          <t>345; 3075</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>23127</t>
+          <t>28046</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4484; 14136</t>
+          <t>4492; 14910</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6173; 18557</t>
+          <t>6287; 19299</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5778; 18392</t>
+          <t>5647; 18297</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9372; 21865</t>
+          <t>11824; 25634</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4570; 14833</t>
+          <t>4076; 14980</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14419; 30731</t>
+          <t>14137; 30575</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9300; 23282</t>
+          <t>9792; 23513</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5009; 12850</t>
+          <t>6284; 14721</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>11181; 26193</t>
+          <t>10902; 25698</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>24158; 44475</t>
+          <t>23894; 44613</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19332; 38315</t>
+          <t>19221; 37717</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>16474; 30813</t>
+          <t>19951; 37767</t>
         </is>
       </c>
     </row>
